--- a/examples/nort_belhaj_analysis/data/nort_round_2.xlsx
+++ b/examples/nort_belhaj_analysis/data/nort_round_2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="423">
   <si>
     <t xml:space="preserve">Test</t>
   </si>
@@ -179,691 +179,694 @@
     <t xml:space="preserve">HCAR1</t>
   </si>
   <si>
+    <t xml:space="preserve">VXFAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age (days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age (months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training (identical objects) T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open-Field-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.08.2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 39.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -/-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aggressive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open-Field-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 38.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open-Field-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 40.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barbed on chest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open-Field-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 41.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lactate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seizure, stereotypic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 43.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stereotypic running</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 42.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 44.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 45.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS: alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 47.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 46.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 48.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 49.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +/-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 51.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 50.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 52.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 53.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 55.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+/-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fighting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 54.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-/-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 56.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 57.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 59.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +/+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 58.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 60.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 61.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 63.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 62.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 64.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 65.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 67.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 66.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 68.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 69.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 71.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 70.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 72.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 73.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 74.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test (novel object) T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 76.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 75.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 77.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 78.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 80.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 79.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 81.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 82.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 84.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 83.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 85.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 86.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 88.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 87.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 89.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 90.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 92.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 91.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 93.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 94.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 96.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 95.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 97.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 98.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 100.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 99.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 101.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 102.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 104.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 103.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 105.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 106.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 108.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 107.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 109.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 110.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 111.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habituation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.08.2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 2.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 1.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 3.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 4.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 6.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 5.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 7.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 8.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 10.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 9.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 11.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 12.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 14.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 13.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 15.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 16.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 18.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 17.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 19.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 20.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 22.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 21.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 23.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 24.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 26.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 25.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 27.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 28.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 30.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 29.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 31.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 32.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 34.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 33.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 35.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 36.szv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORT 30.08.2020 videos\Test 37.szv</t>
+  </si>
+  <si>
     <t xml:space="preserve">5XFAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age (days)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age (months)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training (identical objects) T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open-Field-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.08.2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 39.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -/-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aggressive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open-Field-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 38.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open-Field-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 40.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">barbed on chest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open-Field-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 41.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lactate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seizure, stereotypic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 43.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stereotypic running</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 42.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 44.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 45.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS: alone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 47.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 46.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 48.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 49.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> +/-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 51.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 50.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 52.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 53.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 55.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+/-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fighting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 54.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-/-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 56.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 57.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 59.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> +/+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 58.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 60.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 61.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 63.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 62.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 64.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 65.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 67.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 66.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 68.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 69.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 71.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 70.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 72.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 73.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 74.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test (novel object) T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 76.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 75.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 77.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 78.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 80.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 79.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 81.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 82.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 84.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 83.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 85.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 86.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 88.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 87.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 89.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 90.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 92.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 91.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 93.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 94.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 96.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 95.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 97.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 98.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 100.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 99.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 101.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 102.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 104.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 103.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 105.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 106.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 108.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 107.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 109.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 110.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 111.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Habituation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.08.2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 2.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 1.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 3.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 4.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 6.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 5.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 7.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 8.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 10.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 9.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 11.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 12.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 14.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 13.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 15.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 16.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 18.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 17.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 19.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 20.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 22.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 21.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 23.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 24.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 26.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 25.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 27.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 28.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 30.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 29.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 31.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 32.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 34.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 33.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 35.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 36.szv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORT 30.08.2020 videos\Test 37.szv</t>
   </si>
   <si>
     <t xml:space="preserve">24.11.2020</t>
@@ -2138,6 +2141,44 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="Normal 2" xfId="20"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAAAAAC"/>
+          <bgColor rgb="FF181B28"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2323,7 +2364,7 @@
     <tableColumn id="50" name="Object bias score = (time exploring the object A/total time exploring both objects A1 and B1)*100"/>
     <tableColumn id="51" name="Sex"/>
     <tableColumn id="52" name="HCAR1"/>
-    <tableColumn id="53" name="5XFAD"/>
+    <tableColumn id="53" name="VXFAD"/>
     <tableColumn id="54" name="Age (days)"/>
     <tableColumn id="55" name="Age (months)"/>
     <tableColumn id="56" name="Treatment"/>
@@ -2339,7 +2380,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BN112"/>
-  <sheetFormatPr defaultColWidth="10.84765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.859375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.33"/>
@@ -2348,10 +2389,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="7.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="36.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="10.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="10.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="13.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="15.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="24.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="22.33"/>
@@ -2373,11 +2414,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="3" width="37.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="17.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="3" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="4" width="18.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="4" width="18.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="4" width="23.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="3" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="18.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="3" width="16.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="18.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="3" width="16.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="4" width="19.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="4" width="24.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="3" width="24.83"/>
@@ -2391,7 +2432,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="53" min="51" style="6" width="10.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="6" width="11.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="6" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="6" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="6" width="11.65"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="57" min="57" style="6" width="10.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="6" width="16.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="8" width="9.16"/>
@@ -20783,8 +20824,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -20801,7 +20842,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BN103"/>
-  <sheetFormatPr defaultColWidth="10.84765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.859375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="113" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="114" width="9.33"/>
@@ -20810,10 +20851,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="114" width="11.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="114" width="7.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="114" width="36.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="115" width="10.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="116" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="115" width="10.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="116" width="10.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="116" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="116" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="116" width="13.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="115" width="15.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="113" width="24.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="115" width="22.33"/>
@@ -20835,11 +20876,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="115" width="37.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="113" width="17.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="115" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="116" width="18.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="116" width="18.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="116" width="23.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="115" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="113" width="18.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="115" width="16.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="113" width="18.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="115" width="16.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="116" width="19.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="116" width="24.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="40" style="115" width="24.83"/>
@@ -20852,9 +20893,9 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="53" min="51" style="117" width="10.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="117" width="11.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="117" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="117" width="11.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="117" width="11.65"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="57" min="57" style="117" width="10.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="117" width="19.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="117" width="19.65"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="59" min="59" style="8" width="10.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="8" width="9.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="61" min="61" style="8" width="10.84"/>
@@ -21024,7 +21065,7 @@
         <v>51</v>
       </c>
       <c r="BA1" s="125" t="s">
-        <v>52</v>
+        <v>281</v>
       </c>
       <c r="BB1" s="124" t="s">
         <v>53</v>
@@ -21064,13 +21105,13 @@
         <v>60</v>
       </c>
       <c r="E2" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F2" s="131" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G2" s="131" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H2" s="132" t="n">
         <v>360</v>
@@ -21176,19 +21217,19 @@
       <c r="AQ2" s="26"/>
       <c r="AR2" s="26"/>
       <c r="AS2" s="27" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT2" s="28" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU2" s="28" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV2" s="29" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW2" s="28" t="e">
@@ -21196,7 +21237,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX2" s="27" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY2" s="30" t="s">
@@ -21238,13 +21279,13 @@
         <v>70</v>
       </c>
       <c r="E3" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F3" s="131" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G3" s="131" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H3" s="132" t="n">
         <v>360</v>
@@ -21350,19 +21391,19 @@
       <c r="AQ3" s="26"/>
       <c r="AR3" s="26"/>
       <c r="AS3" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT3" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU3" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV3" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW3" s="135" t="e">
@@ -21370,7 +21411,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX3" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY3" s="30" t="s">
@@ -21412,13 +21453,13 @@
         <v>73</v>
       </c>
       <c r="E4" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F4" s="131" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G4" s="131" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H4" s="132" t="n">
         <v>360</v>
@@ -21524,19 +21565,19 @@
       <c r="AQ4" s="26"/>
       <c r="AR4" s="26"/>
       <c r="AS4" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT4" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU4" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV4" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW4" s="135" t="e">
@@ -21544,7 +21585,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX4" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY4" s="30" t="s">
@@ -21586,13 +21627,13 @@
         <v>77</v>
       </c>
       <c r="E5" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F5" s="131" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G5" s="131" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H5" s="132" t="n">
         <v>360</v>
@@ -21698,19 +21739,19 @@
       <c r="AQ5" s="26"/>
       <c r="AR5" s="26"/>
       <c r="AS5" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT5" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU5" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV5" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW5" s="135" t="e">
@@ -21718,7 +21759,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX5" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY5" s="30" t="s">
@@ -21760,13 +21801,13 @@
         <v>60</v>
       </c>
       <c r="E6" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F6" s="131" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G6" s="131" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H6" s="132" t="n">
         <v>360</v>
@@ -21872,19 +21913,19 @@
       <c r="AQ6" s="26"/>
       <c r="AR6" s="26"/>
       <c r="AS6" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT6" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU6" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV6" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW6" s="135" t="e">
@@ -21892,7 +21933,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX6" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY6" s="30" t="s">
@@ -21932,13 +21973,13 @@
         <v>70</v>
       </c>
       <c r="E7" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F7" s="131" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G7" s="131" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H7" s="132" t="n">
         <v>360</v>
@@ -22044,19 +22085,19 @@
       <c r="AQ7" s="26"/>
       <c r="AR7" s="26"/>
       <c r="AS7" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT7" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU7" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV7" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW7" s="135" t="e">
@@ -22064,7 +22105,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX7" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY7" s="30" t="s">
@@ -22104,13 +22145,13 @@
         <v>73</v>
       </c>
       <c r="E8" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G8" s="131" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H8" s="132" t="n">
         <v>360</v>
@@ -22216,19 +22257,19 @@
       <c r="AQ8" s="26"/>
       <c r="AR8" s="26"/>
       <c r="AS8" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT8" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU8" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV8" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW8" s="135" t="e">
@@ -22236,7 +22277,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX8" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY8" s="30" t="s">
@@ -22278,13 +22319,13 @@
         <v>77</v>
       </c>
       <c r="E9" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F9" s="131" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G9" s="131" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H9" s="132" t="n">
         <v>360</v>
@@ -22390,19 +22431,19 @@
       <c r="AQ9" s="26"/>
       <c r="AR9" s="26"/>
       <c r="AS9" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT9" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU9" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV9" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW9" s="135" t="e">
@@ -22410,7 +22451,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX9" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY9" s="30" t="s">
@@ -22450,13 +22491,13 @@
         <v>60</v>
       </c>
       <c r="E10" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G10" s="131" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H10" s="132" t="n">
         <v>360</v>
@@ -22562,19 +22603,19 @@
       <c r="AQ10" s="26"/>
       <c r="AR10" s="26"/>
       <c r="AS10" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT10" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU10" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV10" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW10" s="135" t="e">
@@ -22582,7 +22623,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX10" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY10" s="30" t="s">
@@ -22622,13 +22663,13 @@
         <v>70</v>
       </c>
       <c r="E11" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F11" s="131" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G11" s="131" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H11" s="132" t="n">
         <v>360</v>
@@ -22734,19 +22775,19 @@
       <c r="AQ11" s="26"/>
       <c r="AR11" s="26"/>
       <c r="AS11" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT11" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU11" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV11" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW11" s="135" t="e">
@@ -22754,7 +22795,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX11" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY11" s="30" t="s">
@@ -22794,13 +22835,13 @@
         <v>73</v>
       </c>
       <c r="E12" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F12" s="131" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G12" s="131" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H12" s="132" t="n">
         <v>360</v>
@@ -22906,19 +22947,19 @@
       <c r="AQ12" s="26"/>
       <c r="AR12" s="26"/>
       <c r="AS12" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT12" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU12" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV12" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW12" s="135" t="e">
@@ -22926,7 +22967,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX12" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY12" s="30" t="s">
@@ -22966,13 +23007,13 @@
         <v>77</v>
       </c>
       <c r="E13" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F13" s="131" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G13" s="131" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H13" s="132" t="n">
         <v>360</v>
@@ -23078,19 +23119,19 @@
       <c r="AQ13" s="26"/>
       <c r="AR13" s="26"/>
       <c r="AS13" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT13" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU13" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV13" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW13" s="135" t="e">
@@ -23098,7 +23139,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX13" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY13" s="30" t="s">
@@ -23123,7 +23164,7 @@
         <v>3</v>
       </c>
       <c r="BF13" s="34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23140,13 +23181,13 @@
         <v>60</v>
       </c>
       <c r="E14" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F14" s="131" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G14" s="131" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H14" s="132" t="n">
         <v>360</v>
@@ -23252,19 +23293,19 @@
       <c r="AQ14" s="26"/>
       <c r="AR14" s="26"/>
       <c r="AS14" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT14" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU14" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV14" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW14" s="135" t="e">
@@ -23272,7 +23313,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX14" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY14" s="30" t="s">
@@ -23312,13 +23353,13 @@
         <v>70</v>
       </c>
       <c r="E15" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G15" s="131" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H15" s="132" t="n">
         <v>360</v>
@@ -23424,19 +23465,19 @@
       <c r="AQ15" s="26"/>
       <c r="AR15" s="26"/>
       <c r="AS15" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT15" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU15" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV15" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW15" s="135" t="e">
@@ -23444,7 +23485,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX15" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY15" s="30" t="s">
@@ -23484,13 +23525,13 @@
         <v>73</v>
       </c>
       <c r="E16" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G16" s="131" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H16" s="132" t="n">
         <v>360</v>
@@ -23596,19 +23637,19 @@
       <c r="AQ16" s="26"/>
       <c r="AR16" s="26"/>
       <c r="AS16" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT16" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU16" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV16" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW16" s="135" t="e">
@@ -23616,7 +23657,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX16" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY16" s="30" t="s">
@@ -23656,13 +23697,13 @@
         <v>77</v>
       </c>
       <c r="E17" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G17" s="131" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H17" s="132" t="n">
         <v>360</v>
@@ -23768,19 +23809,19 @@
       <c r="AQ17" s="26"/>
       <c r="AR17" s="26"/>
       <c r="AS17" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT17" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU17" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV17" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW17" s="135" t="e">
@@ -23788,7 +23829,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX17" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY17" s="30" t="s">
@@ -23830,13 +23871,13 @@
         <v>60</v>
       </c>
       <c r="E18" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F18" s="131" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G18" s="131" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H18" s="132" t="n">
         <v>360</v>
@@ -23942,19 +23983,19 @@
       <c r="AQ18" s="26"/>
       <c r="AR18" s="26"/>
       <c r="AS18" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT18" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU18" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV18" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW18" s="135" t="e">
@@ -23962,7 +24003,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX18" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY18" s="30" t="s">
@@ -24004,13 +24045,13 @@
         <v>70</v>
       </c>
       <c r="E19" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F19" s="131" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G19" s="131" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H19" s="132" t="n">
         <v>360</v>
@@ -24116,19 +24157,19 @@
       <c r="AQ19" s="26"/>
       <c r="AR19" s="26"/>
       <c r="AS19" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT19" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU19" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV19" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW19" s="135" t="e">
@@ -24136,7 +24177,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX19" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY19" s="30" t="s">
@@ -24176,13 +24217,13 @@
         <v>73</v>
       </c>
       <c r="E20" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F20" s="131" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G20" s="131" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H20" s="132" t="n">
         <v>360</v>
@@ -24288,19 +24329,19 @@
       <c r="AQ20" s="26"/>
       <c r="AR20" s="26"/>
       <c r="AS20" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT20" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU20" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV20" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW20" s="135" t="e">
@@ -24308,7 +24349,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX20" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY20" s="30" t="s">
@@ -24350,13 +24391,13 @@
         <v>77</v>
       </c>
       <c r="E21" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F21" s="131" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G21" s="131" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H21" s="132" t="n">
         <v>360</v>
@@ -24462,19 +24503,19 @@
       <c r="AQ21" s="26"/>
       <c r="AR21" s="26"/>
       <c r="AS21" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT21" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU21" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV21" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW21" s="135" t="e">
@@ -24482,7 +24523,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX21" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY21" s="30" t="s">
@@ -24522,13 +24563,13 @@
         <v>60</v>
       </c>
       <c r="E22" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F22" s="131" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G22" s="131" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H22" s="132" t="n">
         <v>360</v>
@@ -24634,19 +24675,19 @@
       <c r="AQ22" s="26"/>
       <c r="AR22" s="26"/>
       <c r="AS22" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT22" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU22" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV22" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW22" s="135" t="e">
@@ -24654,7 +24695,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX22" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY22" s="30" t="s">
@@ -24694,13 +24735,13 @@
         <v>70</v>
       </c>
       <c r="E23" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F23" s="131" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G23" s="131" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H23" s="132" t="n">
         <v>360</v>
@@ -24806,19 +24847,19 @@
       <c r="AQ23" s="26"/>
       <c r="AR23" s="26"/>
       <c r="AS23" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT23" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU23" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV23" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW23" s="135" t="e">
@@ -24826,7 +24867,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX23" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY23" s="30" t="s">
@@ -24866,13 +24907,13 @@
         <v>73</v>
       </c>
       <c r="E24" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F24" s="131" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G24" s="131" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H24" s="132" t="n">
         <v>360</v>
@@ -24978,19 +25019,19 @@
       <c r="AQ24" s="26"/>
       <c r="AR24" s="26"/>
       <c r="AS24" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT24" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU24" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV24" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW24" s="135" t="e">
@@ -24998,7 +25039,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX24" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY24" s="30" t="s">
@@ -25038,13 +25079,13 @@
         <v>77</v>
       </c>
       <c r="E25" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F25" s="131" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G25" s="131" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H25" s="132" t="n">
         <v>360</v>
@@ -25150,19 +25191,19 @@
       <c r="AQ25" s="26"/>
       <c r="AR25" s="26"/>
       <c r="AS25" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT25" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU25" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV25" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW25" s="135" t="e">
@@ -25170,7 +25211,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX25" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY25" s="30" t="s">
@@ -25210,13 +25251,13 @@
         <v>60</v>
       </c>
       <c r="E26" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F26" s="131" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G26" s="131" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H26" s="132" t="n">
         <v>360</v>
@@ -25322,19 +25363,19 @@
       <c r="AQ26" s="26"/>
       <c r="AR26" s="26"/>
       <c r="AS26" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT26" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU26" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV26" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW26" s="135" t="e">
@@ -25342,7 +25383,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX26" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY26" s="30" t="s">
@@ -25382,13 +25423,13 @@
         <v>70</v>
       </c>
       <c r="E27" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F27" s="131" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G27" s="131" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H27" s="132" t="n">
         <v>360</v>
@@ -25494,19 +25535,19 @@
       <c r="AQ27" s="26"/>
       <c r="AR27" s="26"/>
       <c r="AS27" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT27" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU27" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV27" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW27" s="135" t="e">
@@ -25514,7 +25555,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX27" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY27" s="30" t="s">
@@ -25554,13 +25595,13 @@
         <v>73</v>
       </c>
       <c r="E28" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F28" s="131" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G28" s="131" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H28" s="132" t="n">
         <v>360</v>
@@ -25666,19 +25707,19 @@
       <c r="AQ28" s="26"/>
       <c r="AR28" s="26"/>
       <c r="AS28" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT28" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU28" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV28" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW28" s="135" t="e">
@@ -25686,7 +25727,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX28" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY28" s="30" t="s">
@@ -25728,13 +25769,13 @@
         <v>77</v>
       </c>
       <c r="E29" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F29" s="131" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G29" s="131" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H29" s="132" t="n">
         <v>360</v>
@@ -25840,19 +25881,19 @@
       <c r="AQ29" s="26"/>
       <c r="AR29" s="26"/>
       <c r="AS29" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT29" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU29" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV29" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW29" s="135" t="e">
@@ -25860,7 +25901,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX29" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY29" s="30" t="s">
@@ -25900,13 +25941,13 @@
         <v>60</v>
       </c>
       <c r="E30" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F30" s="131" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G30" s="131" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H30" s="132" t="n">
         <v>360</v>
@@ -26012,19 +26053,19 @@
       <c r="AQ30" s="26"/>
       <c r="AR30" s="26"/>
       <c r="AS30" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT30" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU30" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV30" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW30" s="135" t="e">
@@ -26032,7 +26073,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX30" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY30" s="30" t="s">
@@ -26072,13 +26113,13 @@
         <v>70</v>
       </c>
       <c r="E31" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F31" s="131" t="s">
         <v>155</v>
       </c>
       <c r="G31" s="131" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H31" s="132" t="n">
         <v>360</v>
@@ -26184,19 +26225,19 @@
       <c r="AQ31" s="26"/>
       <c r="AR31" s="26"/>
       <c r="AS31" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT31" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU31" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV31" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW31" s="135" t="e">
@@ -26204,7 +26245,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX31" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY31" s="30" t="s">
@@ -26244,13 +26285,13 @@
         <v>73</v>
       </c>
       <c r="E32" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F32" s="131" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G32" s="131" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H32" s="132" t="n">
         <v>360</v>
@@ -26356,19 +26397,19 @@
       <c r="AQ32" s="26"/>
       <c r="AR32" s="26"/>
       <c r="AS32" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT32" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU32" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV32" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW32" s="135" t="e">
@@ -26376,7 +26417,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX32" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY32" s="30" t="s">
@@ -26416,13 +26457,13 @@
         <v>77</v>
       </c>
       <c r="E33" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F33" s="131" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G33" s="131" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H33" s="132" t="n">
         <v>360</v>
@@ -26526,19 +26567,19 @@
       <c r="AQ33" s="26"/>
       <c r="AR33" s="26"/>
       <c r="AS33" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT33" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU33" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV33" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW33" s="135" t="e">
@@ -26546,7 +26587,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX33" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY33" s="30" t="s">
@@ -26586,13 +26627,13 @@
         <v>60</v>
       </c>
       <c r="E34" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F34" s="131" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G34" s="131" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H34" s="132" t="n">
         <v>360</v>
@@ -26698,19 +26739,19 @@
       <c r="AQ34" s="26"/>
       <c r="AR34" s="26"/>
       <c r="AS34" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT34" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU34" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV34" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW34" s="135" t="e">
@@ -26718,7 +26759,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX34" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY34" s="30" t="s">
@@ -26758,13 +26799,13 @@
         <v>70</v>
       </c>
       <c r="E35" s="131" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F35" s="131" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G35" s="131" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H35" s="132" t="n">
         <v>360</v>
@@ -26870,19 +26911,19 @@
       <c r="AQ35" s="26"/>
       <c r="AR35" s="26"/>
       <c r="AS35" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT35" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU35" s="135" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV35" s="136" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW35" s="135" t="e">
@@ -26890,7 +26931,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX35" s="135" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY35" s="30" t="s">
@@ -26930,13 +26971,13 @@
         <v>60</v>
       </c>
       <c r="E36" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F36" s="138" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G36" s="138" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H36" s="139" t="n">
         <v>360</v>
@@ -27042,19 +27083,19 @@
       <c r="AQ36" s="52"/>
       <c r="AR36" s="52"/>
       <c r="AS36" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT36" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU36" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV36" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW36" s="142" t="e">
@@ -27062,7 +27103,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX36" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY36" s="57" t="s">
@@ -27104,13 +27145,13 @@
         <v>70</v>
       </c>
       <c r="E37" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F37" s="138" t="s">
         <v>173</v>
       </c>
       <c r="G37" s="138" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H37" s="139" t="n">
         <v>360</v>
@@ -27214,19 +27255,19 @@
       <c r="AQ37" s="52"/>
       <c r="AR37" s="52"/>
       <c r="AS37" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT37" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU37" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV37" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW37" s="142" t="e">
@@ -27234,7 +27275,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX37" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY37" s="57" t="s">
@@ -27276,13 +27317,13 @@
         <v>73</v>
       </c>
       <c r="E38" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F38" s="138" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G38" s="138" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H38" s="139" t="n">
         <v>360</v>
@@ -27388,19 +27429,19 @@
       <c r="AQ38" s="52"/>
       <c r="AR38" s="52"/>
       <c r="AS38" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT38" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU38" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV38" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW38" s="142" t="e">
@@ -27408,7 +27449,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX38" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY38" s="57" t="s">
@@ -27450,13 +27491,13 @@
         <v>77</v>
       </c>
       <c r="E39" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F39" s="138" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G39" s="138" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H39" s="139" t="n">
         <v>360</v>
@@ -27562,19 +27603,19 @@
       <c r="AQ39" s="52"/>
       <c r="AR39" s="52"/>
       <c r="AS39" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT39" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU39" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV39" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW39" s="142" t="e">
@@ -27582,7 +27623,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX39" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY39" s="57" t="s">
@@ -27624,13 +27665,13 @@
         <v>60</v>
       </c>
       <c r="E40" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F40" s="138" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G40" s="138" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H40" s="139" t="n">
         <v>360</v>
@@ -27736,19 +27777,19 @@
       <c r="AQ40" s="52"/>
       <c r="AR40" s="52"/>
       <c r="AS40" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT40" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU40" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV40" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW40" s="142" t="e">
@@ -27756,7 +27797,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX40" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY40" s="57" t="s">
@@ -27796,13 +27837,13 @@
         <v>70</v>
       </c>
       <c r="E41" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F41" s="138" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G41" s="138" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H41" s="139" t="n">
         <v>360</v>
@@ -27908,19 +27949,19 @@
       <c r="AQ41" s="52"/>
       <c r="AR41" s="52"/>
       <c r="AS41" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT41" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU41" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV41" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW41" s="142" t="e">
@@ -27928,7 +27969,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX41" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY41" s="57" t="s">
@@ -27968,13 +28009,13 @@
         <v>73</v>
       </c>
       <c r="E42" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F42" s="138" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G42" s="138" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H42" s="139" t="n">
         <v>360</v>
@@ -28080,19 +28121,19 @@
       <c r="AQ42" s="52"/>
       <c r="AR42" s="52"/>
       <c r="AS42" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT42" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU42" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV42" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW42" s="142" t="e">
@@ -28100,7 +28141,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX42" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY42" s="57" t="s">
@@ -28142,13 +28183,13 @@
         <v>77</v>
       </c>
       <c r="E43" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F43" s="138" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G43" s="138" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H43" s="139" t="n">
         <v>360</v>
@@ -28254,19 +28295,19 @@
       <c r="AQ43" s="52"/>
       <c r="AR43" s="52"/>
       <c r="AS43" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT43" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU43" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV43" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW43" s="142" t="e">
@@ -28274,7 +28315,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX43" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY43" s="57" t="s">
@@ -28314,13 +28355,13 @@
         <v>60</v>
       </c>
       <c r="E44" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F44" s="138" t="s">
         <v>183</v>
       </c>
       <c r="G44" s="138" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H44" s="139" t="n">
         <v>360</v>
@@ -28426,19 +28467,19 @@
       <c r="AQ44" s="52"/>
       <c r="AR44" s="52"/>
       <c r="AS44" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT44" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU44" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV44" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW44" s="142" t="e">
@@ -28446,7 +28487,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX44" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY44" s="57" t="s">
@@ -28486,13 +28527,13 @@
         <v>70</v>
       </c>
       <c r="E45" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F45" s="138" t="s">
         <v>183</v>
       </c>
       <c r="G45" s="138" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H45" s="139" t="n">
         <v>360</v>
@@ -28598,19 +28639,19 @@
       <c r="AQ45" s="52"/>
       <c r="AR45" s="52"/>
       <c r="AS45" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT45" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU45" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV45" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW45" s="142" t="e">
@@ -28618,7 +28659,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX45" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY45" s="57" t="s">
@@ -28658,13 +28699,13 @@
         <v>73</v>
       </c>
       <c r="E46" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F46" s="138" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G46" s="138" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H46" s="139" t="n">
         <v>360</v>
@@ -28770,19 +28811,19 @@
       <c r="AQ46" s="52"/>
       <c r="AR46" s="52"/>
       <c r="AS46" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT46" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU46" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV46" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW46" s="142" t="e">
@@ -28790,7 +28831,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX46" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY46" s="57" t="s">
@@ -28830,13 +28871,13 @@
         <v>77</v>
       </c>
       <c r="E47" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F47" s="138" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G47" s="138" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H47" s="139" t="n">
         <v>360</v>
@@ -28942,19 +28983,19 @@
       <c r="AQ47" s="52"/>
       <c r="AR47" s="52"/>
       <c r="AS47" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT47" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU47" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV47" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW47" s="142" t="e">
@@ -28962,7 +29003,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX47" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY47" s="57" t="s">
@@ -28987,7 +29028,7 @@
         <v>3</v>
       </c>
       <c r="BF47" s="61" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29004,13 +29045,13 @@
         <v>60</v>
       </c>
       <c r="E48" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F48" s="138" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G48" s="138" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H48" s="139" t="n">
         <v>360</v>
@@ -29116,19 +29157,19 @@
       <c r="AQ48" s="52"/>
       <c r="AR48" s="52"/>
       <c r="AS48" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT48" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU48" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV48" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW48" s="142" t="e">
@@ -29136,7 +29177,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX48" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY48" s="57" t="s">
@@ -29176,13 +29217,13 @@
         <v>70</v>
       </c>
       <c r="E49" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F49" s="138" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G49" s="138" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H49" s="139" t="n">
         <v>360</v>
@@ -29288,19 +29329,19 @@
       <c r="AQ49" s="52"/>
       <c r="AR49" s="52"/>
       <c r="AS49" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT49" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU49" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV49" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW49" s="142" t="e">
@@ -29308,7 +29349,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX49" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY49" s="57" t="s">
@@ -29348,13 +29389,13 @@
         <v>73</v>
       </c>
       <c r="E50" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F50" s="138" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G50" s="138" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H50" s="139" t="n">
         <v>360</v>
@@ -29460,19 +29501,19 @@
       <c r="AQ50" s="52"/>
       <c r="AR50" s="52"/>
       <c r="AS50" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT50" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU50" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV50" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW50" s="142" t="e">
@@ -29480,7 +29521,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX50" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY50" s="57" t="s">
@@ -29520,13 +29561,13 @@
         <v>77</v>
       </c>
       <c r="E51" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F51" s="138" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G51" s="138" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H51" s="139" t="n">
         <v>360</v>
@@ -29632,19 +29673,19 @@
       <c r="AQ51" s="52"/>
       <c r="AR51" s="52"/>
       <c r="AS51" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT51" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU51" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV51" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW51" s="142" t="e">
@@ -29652,7 +29693,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX51" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY51" s="57" t="s">
@@ -29694,13 +29735,13 @@
         <v>60</v>
       </c>
       <c r="E52" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F52" s="138" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G52" s="138" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H52" s="139" t="n">
         <v>360</v>
@@ -29806,19 +29847,19 @@
       <c r="AQ52" s="52"/>
       <c r="AR52" s="52"/>
       <c r="AS52" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT52" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU52" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV52" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW52" s="142" t="e">
@@ -29826,7 +29867,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX52" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY52" s="57" t="s">
@@ -29868,13 +29909,13 @@
         <v>70</v>
       </c>
       <c r="E53" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F53" s="138" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G53" s="138" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H53" s="139" t="n">
         <v>360</v>
@@ -29980,19 +30021,19 @@
       <c r="AQ53" s="52"/>
       <c r="AR53" s="52"/>
       <c r="AS53" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT53" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU53" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV53" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW53" s="142" t="e">
@@ -30000,7 +30041,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX53" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY53" s="57" t="s">
@@ -30040,13 +30081,13 @@
         <v>73</v>
       </c>
       <c r="E54" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F54" s="138" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G54" s="138" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H54" s="139" t="n">
         <v>360</v>
@@ -30152,19 +30193,19 @@
       <c r="AQ54" s="52"/>
       <c r="AR54" s="52"/>
       <c r="AS54" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT54" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU54" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV54" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW54" s="142" t="e">
@@ -30172,7 +30213,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX54" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY54" s="57" t="s">
@@ -30214,13 +30255,13 @@
         <v>77</v>
       </c>
       <c r="E55" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F55" s="138" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G55" s="138" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H55" s="139" t="n">
         <v>360</v>
@@ -30326,19 +30367,19 @@
       <c r="AQ55" s="52"/>
       <c r="AR55" s="52"/>
       <c r="AS55" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT55" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU55" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV55" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW55" s="142" t="e">
@@ -30346,7 +30387,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX55" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY55" s="57" t="s">
@@ -30386,13 +30427,13 @@
         <v>60</v>
       </c>
       <c r="E56" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F56" s="138" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G56" s="138" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H56" s="139" t="n">
         <v>360</v>
@@ -30498,19 +30539,19 @@
       <c r="AQ56" s="52"/>
       <c r="AR56" s="52"/>
       <c r="AS56" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT56" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU56" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV56" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW56" s="142" t="e">
@@ -30518,7 +30559,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX56" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY56" s="57" t="s">
@@ -30558,13 +30599,13 @@
         <v>70</v>
       </c>
       <c r="E57" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F57" s="138" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G57" s="138" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H57" s="139" t="n">
         <v>360</v>
@@ -30670,19 +30711,19 @@
       <c r="AQ57" s="52"/>
       <c r="AR57" s="52"/>
       <c r="AS57" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT57" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU57" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV57" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW57" s="142" t="e">
@@ -30690,7 +30731,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX57" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY57" s="57" t="s">
@@ -30730,13 +30771,13 @@
         <v>73</v>
       </c>
       <c r="E58" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F58" s="138" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G58" s="138" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H58" s="139" t="n">
         <v>360</v>
@@ -30842,19 +30883,19 @@
       <c r="AQ58" s="52"/>
       <c r="AR58" s="52"/>
       <c r="AS58" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT58" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU58" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV58" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW58" s="142" t="e">
@@ -30862,7 +30903,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX58" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY58" s="57" t="s">
@@ -30902,13 +30943,13 @@
         <v>77</v>
       </c>
       <c r="E59" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F59" s="138" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G59" s="138" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H59" s="139" t="n">
         <v>360</v>
@@ -31014,19 +31055,19 @@
       <c r="AQ59" s="52"/>
       <c r="AR59" s="52"/>
       <c r="AS59" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT59" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU59" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV59" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW59" s="142" t="e">
@@ -31034,7 +31075,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX59" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY59" s="57" t="s">
@@ -31074,13 +31115,13 @@
         <v>60</v>
       </c>
       <c r="E60" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F60" s="138" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G60" s="138" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H60" s="139" t="n">
         <v>360</v>
@@ -31186,19 +31227,19 @@
       <c r="AQ60" s="52"/>
       <c r="AR60" s="52"/>
       <c r="AS60" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT60" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU60" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV60" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW60" s="142" t="e">
@@ -31206,7 +31247,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX60" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY60" s="57" t="s">
@@ -31246,13 +31287,13 @@
         <v>70</v>
       </c>
       <c r="E61" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F61" s="138" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G61" s="138" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H61" s="139" t="n">
         <v>360</v>
@@ -31358,19 +31399,19 @@
       <c r="AQ61" s="52"/>
       <c r="AR61" s="52"/>
       <c r="AS61" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT61" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU61" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV61" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW61" s="142" t="e">
@@ -31378,7 +31419,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX61" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY61" s="57" t="s">
@@ -31418,13 +31459,13 @@
         <v>73</v>
       </c>
       <c r="E62" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F62" s="138" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G62" s="138" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H62" s="139" t="n">
         <v>360</v>
@@ -31530,19 +31571,19 @@
       <c r="AQ62" s="52"/>
       <c r="AR62" s="52"/>
       <c r="AS62" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT62" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU62" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV62" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW62" s="142" t="e">
@@ -31550,7 +31591,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX62" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY62" s="57" t="s">
@@ -31592,13 +31633,13 @@
         <v>77</v>
       </c>
       <c r="E63" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F63" s="138" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G63" s="138" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H63" s="139" t="n">
         <v>360</v>
@@ -31704,19 +31745,19 @@
       <c r="AQ63" s="52"/>
       <c r="AR63" s="52"/>
       <c r="AS63" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT63" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU63" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV63" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW63" s="142" t="e">
@@ -31724,7 +31765,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX63" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY63" s="57" t="s">
@@ -31764,13 +31805,13 @@
         <v>60</v>
       </c>
       <c r="E64" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F64" s="138" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G64" s="138" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H64" s="139" t="n">
         <v>360</v>
@@ -31876,19 +31917,19 @@
       <c r="AQ64" s="52"/>
       <c r="AR64" s="52"/>
       <c r="AS64" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT64" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU64" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV64" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW64" s="142" t="e">
@@ -31896,7 +31937,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX64" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY64" s="57" t="s">
@@ -31936,13 +31977,13 @@
         <v>70</v>
       </c>
       <c r="E65" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F65" s="138" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G65" s="138" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H65" s="139" t="n">
         <v>360</v>
@@ -32048,19 +32089,19 @@
       <c r="AQ65" s="52"/>
       <c r="AR65" s="52"/>
       <c r="AS65" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT65" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU65" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV65" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW65" s="142" t="e">
@@ -32068,7 +32109,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX65" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY65" s="57" t="s">
@@ -32108,13 +32149,13 @@
         <v>73</v>
       </c>
       <c r="E66" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F66" s="138" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G66" s="138" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H66" s="139" t="n">
         <v>360</v>
@@ -32220,19 +32261,19 @@
       <c r="AQ66" s="52"/>
       <c r="AR66" s="52"/>
       <c r="AS66" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT66" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU66" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV66" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW66" s="142" t="e">
@@ -32240,7 +32281,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX66" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY66" s="57" t="s">
@@ -32280,13 +32321,13 @@
         <v>77</v>
       </c>
       <c r="E67" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F67" s="138" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G67" s="138" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H67" s="139" t="n">
         <v>360</v>
@@ -32392,19 +32433,19 @@
       <c r="AQ67" s="52"/>
       <c r="AR67" s="52"/>
       <c r="AS67" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT67" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU67" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV67" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW67" s="142" t="e">
@@ -32412,7 +32453,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX67" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY67" s="57" t="s">
@@ -32452,13 +32493,13 @@
         <v>60</v>
       </c>
       <c r="E68" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F68" s="138" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G68" s="138" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H68" s="139" t="n">
         <v>360</v>
@@ -32564,19 +32605,19 @@
       <c r="AQ68" s="52"/>
       <c r="AR68" s="52"/>
       <c r="AS68" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT68" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU68" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV68" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW68" s="142" t="e">
@@ -32584,7 +32625,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX68" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY68" s="57" t="s">
@@ -32624,13 +32665,13 @@
         <v>70</v>
       </c>
       <c r="E69" s="138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F69" s="138" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G69" s="138" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H69" s="139" t="n">
         <v>360</v>
@@ -32736,19 +32777,19 @@
       <c r="AQ69" s="52"/>
       <c r="AR69" s="52"/>
       <c r="AS69" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT69" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU69" s="142" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV69" s="143" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW69" s="142" t="e">
@@ -32756,7 +32797,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX69" s="142" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY69" s="57" t="s">
@@ -32796,13 +32837,13 @@
         <v>60</v>
       </c>
       <c r="E70" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F70" s="145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G70" s="145" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H70" s="146" t="n">
         <v>300</v>
@@ -32920,19 +32961,19 @@
         <v>0.829224401655569</v>
       </c>
       <c r="AS70" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT70" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU70" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV70" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW70" s="149" t="e">
@@ -32940,7 +32981,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX70" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY70" s="82" t="s">
@@ -32982,13 +33023,13 @@
         <v>70</v>
       </c>
       <c r="E71" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F71" s="145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G71" s="145" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H71" s="146" t="n">
         <v>300</v>
@@ -33106,19 +33147,19 @@
         <v>0.763527054108216</v>
       </c>
       <c r="AS71" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT71" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU71" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV71" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW71" s="149" t="e">
@@ -33126,7 +33167,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX71" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY71" s="82" t="s">
@@ -33168,13 +33209,13 @@
         <v>73</v>
       </c>
       <c r="E72" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F72" s="145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G72" s="145" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H72" s="146" t="n">
         <v>300</v>
@@ -33292,19 +33333,19 @@
         <v>0.660590364246107</v>
       </c>
       <c r="AS72" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT72" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU72" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV72" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW72" s="149" t="e">
@@ -33312,7 +33353,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX72" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY72" s="82" t="s">
@@ -33354,13 +33395,13 @@
         <v>77</v>
       </c>
       <c r="E73" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F73" s="145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G73" s="145" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H73" s="146" t="n">
         <v>300</v>
@@ -33478,19 +33519,19 @@
         <v>0.864494551731579</v>
       </c>
       <c r="AS73" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT73" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU73" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV73" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW73" s="149" t="e">
@@ -33498,7 +33539,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX73" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY73" s="82" t="s">
@@ -33540,13 +33581,13 @@
         <v>60</v>
       </c>
       <c r="E74" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F74" s="145" t="s">
         <v>226</v>
       </c>
       <c r="G74" s="145" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H74" s="146" t="n">
         <v>300</v>
@@ -33664,19 +33705,19 @@
         <v>0.913785224676314</v>
       </c>
       <c r="AS74" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT74" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU74" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV74" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW74" s="149" t="e">
@@ -33684,7 +33725,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX74" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY74" s="82" t="s">
@@ -33724,13 +33765,13 @@
         <v>70</v>
       </c>
       <c r="E75" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F75" s="145" t="s">
         <v>226</v>
       </c>
       <c r="G75" s="145" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H75" s="146" t="n">
         <v>300</v>
@@ -33848,19 +33889,19 @@
         <v>0.797552714956845</v>
       </c>
       <c r="AS75" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT75" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU75" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV75" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW75" s="149" t="e">
@@ -33868,7 +33909,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX75" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY75" s="82" t="s">
@@ -33908,13 +33949,13 @@
         <v>73</v>
       </c>
       <c r="E76" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F76" s="145" t="s">
         <v>226</v>
       </c>
       <c r="G76" s="145" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H76" s="146" t="n">
         <v>300</v>
@@ -34032,19 +34073,19 @@
         <v>0.79643699240241</v>
       </c>
       <c r="AS76" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT76" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU76" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV76" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW76" s="149" t="e">
@@ -34052,7 +34093,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX76" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY76" s="82" t="s">
@@ -34094,13 +34135,13 @@
         <v>77</v>
       </c>
       <c r="E77" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F77" s="145" t="s">
         <v>226</v>
       </c>
       <c r="G77" s="145" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H77" s="146" t="n">
         <v>300</v>
@@ -34218,19 +34259,19 @@
         <v>0.740560140035009</v>
       </c>
       <c r="AS77" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT77" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU77" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV77" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW77" s="149" t="e">
@@ -34238,7 +34279,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX77" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY77" s="82" t="s">
@@ -34278,13 +34319,13 @@
         <v>60</v>
       </c>
       <c r="E78" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F78" s="145" t="s">
         <v>235</v>
       </c>
       <c r="G78" s="145" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H78" s="146" t="n">
         <v>300</v>
@@ -34402,19 +34443,19 @@
         <v>0.908972691807542</v>
       </c>
       <c r="AS78" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT78" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU78" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV78" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW78" s="149" t="e">
@@ -34422,7 +34463,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX78" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY78" s="82" t="s">
@@ -34462,13 +34503,13 @@
         <v>70</v>
       </c>
       <c r="E79" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F79" s="145" t="s">
         <v>235</v>
       </c>
       <c r="G79" s="145" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H79" s="146" t="n">
         <v>300</v>
@@ -34586,19 +34627,19 @@
         <v>0.834804708400214</v>
       </c>
       <c r="AS79" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT79" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU79" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV79" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW79" s="149" t="e">
@@ -34606,7 +34647,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX79" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY79" s="82" t="s">
@@ -34646,13 +34687,13 @@
         <v>73</v>
       </c>
       <c r="E80" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F80" s="145" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G80" s="145" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H80" s="146" t="n">
         <v>300</v>
@@ -34770,19 +34811,19 @@
         <v>0.904899731238371</v>
       </c>
       <c r="AS80" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT80" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU80" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV80" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW80" s="149" t="e">
@@ -34790,7 +34831,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX80" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY80" s="82" t="s">
@@ -34830,13 +34871,13 @@
         <v>77</v>
       </c>
       <c r="E81" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F81" s="145" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G81" s="145" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H81" s="146" t="n">
         <v>300</v>
@@ -34954,19 +34995,19 @@
         <v>0.63962287557375</v>
       </c>
       <c r="AS81" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT81" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU81" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV81" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW81" s="149" t="e">
@@ -34974,7 +35015,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX81" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY81" s="82" t="s">
@@ -34999,7 +35040,7 @@
         <v>3</v>
       </c>
       <c r="BF81" s="86" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35016,13 +35057,13 @@
         <v>60</v>
       </c>
       <c r="E82" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F82" s="145" t="s">
         <v>241</v>
       </c>
       <c r="G82" s="145" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H82" s="146" t="n">
         <v>300</v>
@@ -35140,19 +35181,19 @@
         <v>0.825948358304112</v>
       </c>
       <c r="AS82" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT82" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU82" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV82" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW82" s="149" t="e">
@@ -35160,7 +35201,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX82" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY82" s="82" t="s">
@@ -35200,13 +35241,13 @@
         <v>70</v>
       </c>
       <c r="E83" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F83" s="145" t="s">
         <v>241</v>
       </c>
       <c r="G83" s="145" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H83" s="146" t="n">
         <v>300</v>
@@ -35324,19 +35365,19 @@
         <v>0.699097574732093</v>
       </c>
       <c r="AS83" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT83" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU83" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV83" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW83" s="149" t="e">
@@ -35344,7 +35385,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX83" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY83" s="82" t="s">
@@ -35384,13 +35425,13 @@
         <v>73</v>
       </c>
       <c r="E84" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F84" s="145" t="s">
         <v>241</v>
       </c>
       <c r="G84" s="145" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H84" s="146" t="n">
         <v>300</v>
@@ -35508,19 +35549,19 @@
         <v>0.782533754668199</v>
       </c>
       <c r="AS84" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT84" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU84" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV84" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW84" s="149" t="e">
@@ -35528,7 +35569,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX84" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY84" s="82" t="s">
@@ -35568,13 +35609,13 @@
         <v>77</v>
       </c>
       <c r="E85" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F85" s="145" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G85" s="145" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H85" s="146" t="n">
         <v>300</v>
@@ -35692,19 +35733,19 @@
         <v>0.870120394016782</v>
       </c>
       <c r="AS85" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT85" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU85" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV85" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW85" s="149" t="e">
@@ -35712,7 +35753,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX85" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY85" s="82" t="s">
@@ -35754,13 +35795,13 @@
         <v>60</v>
       </c>
       <c r="E86" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F86" s="145" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G86" s="145" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H86" s="146" t="n">
         <v>300</v>
@@ -35878,19 +35919,19 @@
         <v>0.739113222486144</v>
       </c>
       <c r="AS86" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT86" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU86" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV86" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW86" s="149" t="e">
@@ -35898,7 +35939,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX86" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY86" s="82" t="s">
@@ -35940,13 +35981,13 @@
         <v>70</v>
       </c>
       <c r="E87" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F87" s="145" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G87" s="145" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H87" s="146" t="n">
         <v>300</v>
@@ -36064,19 +36105,19 @@
         <v>0.8285835814547</v>
       </c>
       <c r="AS87" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT87" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU87" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV87" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW87" s="149" t="e">
@@ -36084,7 +36125,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX87" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY87" s="82" t="s">
@@ -36124,13 +36165,13 @@
         <v>73</v>
       </c>
       <c r="E88" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F88" s="145" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G88" s="145" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H88" s="146" t="n">
         <v>300</v>
@@ -36248,19 +36289,19 @@
         <v>0.888109000825764</v>
       </c>
       <c r="AS88" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT88" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU88" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV88" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW88" s="149" t="e">
@@ -36268,7 +36309,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX88" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY88" s="82" t="s">
@@ -36310,13 +36351,13 @@
         <v>77</v>
       </c>
       <c r="E89" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F89" s="145" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G89" s="145" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H89" s="146" t="n">
         <v>300</v>
@@ -36434,19 +36475,19 @@
         <v>0.880041544054007</v>
       </c>
       <c r="AS89" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT89" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU89" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV89" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW89" s="149" t="e">
@@ -36454,7 +36495,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX89" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY89" s="82" t="s">
@@ -36494,13 +36535,13 @@
         <v>60</v>
       </c>
       <c r="E90" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F90" s="145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G90" s="145" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H90" s="146" t="n">
         <v>300</v>
@@ -36618,19 +36659,19 @@
         <v>0.739978331527627</v>
       </c>
       <c r="AS90" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT90" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU90" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV90" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW90" s="149" t="e">
@@ -36638,7 +36679,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX90" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY90" s="82" t="s">
@@ -36678,13 +36719,13 @@
         <v>70</v>
       </c>
       <c r="E91" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F91" s="145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G91" s="145" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H91" s="146" t="n">
         <v>300</v>
@@ -36802,19 +36843,19 @@
         <v>0.683501184834123</v>
       </c>
       <c r="AS91" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT91" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU91" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV91" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW91" s="149" t="e">
@@ -36822,7 +36863,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX91" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY91" s="82" t="s">
@@ -36862,13 +36903,13 @@
         <v>73</v>
       </c>
       <c r="E92" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F92" s="145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G92" s="145" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H92" s="146" t="n">
         <v>300</v>
@@ -36986,19 +37027,19 @@
         <v>0.892743362831858</v>
       </c>
       <c r="AS92" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT92" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU92" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV92" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW92" s="149" t="e">
@@ -37006,7 +37047,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX92" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY92" s="82" t="s">
@@ -37046,13 +37087,13 @@
         <v>77</v>
       </c>
       <c r="E93" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F93" s="145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G93" s="145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H93" s="146" t="n">
         <v>300</v>
@@ -37170,19 +37211,19 @@
         <v>0.87407882089074</v>
       </c>
       <c r="AS93" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT93" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU93" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV93" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW93" s="149" t="e">
@@ -37190,7 +37231,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX93" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY93" s="82" t="s">
@@ -37230,13 +37271,13 @@
         <v>60</v>
       </c>
       <c r="E94" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F94" s="145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G94" s="145" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H94" s="146" t="n">
         <v>300</v>
@@ -37354,19 +37395,19 @@
         <v>0.827238887672433</v>
       </c>
       <c r="AS94" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT94" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU94" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV94" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW94" s="149" t="e">
@@ -37374,7 +37415,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX94" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY94" s="82" t="s">
@@ -37414,13 +37455,13 @@
         <v>70</v>
       </c>
       <c r="E95" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F95" s="145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G95" s="145" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H95" s="146" t="n">
         <v>300</v>
@@ -37538,19 +37579,19 @@
         <v>0.908047155304972</v>
       </c>
       <c r="AS95" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT95" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU95" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV95" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW95" s="149" t="e">
@@ -37558,7 +37599,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX95" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY95" s="82" t="s">
@@ -37598,13 +37639,13 @@
         <v>73</v>
       </c>
       <c r="E96" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F96" s="145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G96" s="145" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H96" s="146" t="n">
         <v>300</v>
@@ -37722,19 +37763,19 @@
         <v>0.801399354144241</v>
       </c>
       <c r="AS96" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT96" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU96" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV96" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW96" s="149" t="e">
@@ -37742,7 +37783,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX96" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY96" s="82" t="s">
@@ -37784,13 +37825,13 @@
         <v>77</v>
       </c>
       <c r="E97" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F97" s="145" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G97" s="145" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H97" s="146" t="n">
         <v>300</v>
@@ -37908,19 +37949,19 @@
         <v>0.846634146341463</v>
       </c>
       <c r="AS97" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT97" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU97" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV97" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW97" s="149" t="e">
@@ -37928,7 +37969,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX97" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY97" s="82" t="s">
@@ -37968,13 +38009,13 @@
         <v>60</v>
       </c>
       <c r="E98" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F98" s="145" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G98" s="145" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H98" s="146" t="n">
         <v>300</v>
@@ -38092,19 +38133,19 @@
         <v>0.874292007551919</v>
       </c>
       <c r="AS98" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT98" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU98" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV98" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW98" s="149" t="e">
@@ -38112,7 +38153,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX98" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY98" s="82" t="s">
@@ -38152,13 +38193,13 @@
         <v>70</v>
       </c>
       <c r="E99" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F99" s="145" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G99" s="145" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H99" s="146" t="n">
         <v>300</v>
@@ -38276,19 +38317,19 @@
         <v>0.838533612298736</v>
       </c>
       <c r="AS99" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT99" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU99" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV99" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW99" s="149" t="e">
@@ -38296,7 +38337,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX99" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY99" s="82" t="s">
@@ -38336,13 +38377,13 @@
         <v>73</v>
       </c>
       <c r="E100" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F100" s="145" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G100" s="145" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H100" s="146" t="n">
         <v>300</v>
@@ -38460,19 +38501,19 @@
         <v>0.94955268389662</v>
       </c>
       <c r="AS100" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT100" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU100" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV100" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW100" s="149" t="e">
@@ -38480,7 +38521,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX100" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY100" s="82" t="s">
@@ -38520,13 +38561,13 @@
         <v>77</v>
       </c>
       <c r="E101" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F101" s="145" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G101" s="145" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H101" s="146" t="n">
         <v>300</v>
@@ -38644,19 +38685,19 @@
         <v>0.914384123339347</v>
       </c>
       <c r="AS101" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT101" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU101" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV101" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW101" s="149" t="e">
@@ -38664,7 +38705,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX101" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY101" s="82" t="s">
@@ -38704,13 +38745,13 @@
         <v>60</v>
       </c>
       <c r="E102" s="145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F102" s="145" t="s">
         <v>173</v>
       </c>
       <c r="G102" s="145" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H102" s="146" t="n">
         <v>300</v>
@@ -38828,19 +38869,19 @@
         <v>0.829888935751441</v>
       </c>
       <c r="AS102" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT102" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU102" s="149" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV102" s="150" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW102" s="149" t="e">
@@ -38848,7 +38889,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX102" s="149" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY102" s="82" t="s">
@@ -38888,13 +38929,13 @@
         <v>70</v>
       </c>
       <c r="E103" s="152" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F103" s="152" t="s">
         <v>173</v>
       </c>
       <c r="G103" s="152" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H103" s="153" t="n">
         <v>300</v>
@@ -39010,19 +39051,19 @@
         <v>0.832338578404775</v>
       </c>
       <c r="AS103" s="156" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AT103" s="156" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AU103" s="156" t="e">
-        <f aca="false">[1]!Table2[[#this row],[object_b_._head_time]]-[1]!Table2[[#this row],[object_a_._head_time]]</f>
+        <f aca="false">[1]!table2[[#this row],[object_b_._head_time]]-[1]!table2[[#this row],[object_a_._head_time]]</f>
         <v>#N/A</v>
       </c>
       <c r="AV103" s="157" t="e">
-        <f aca="false">[1]!Table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!Table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
+        <f aca="false">[1]!table2[[#this row],[d1: absolute discrimination measure (D1 = B2- A2)]]/[1]!table2[[#this row],[e2: total exploration time in second trial E2 ( E2 = A2 + B2)]]</f>
         <v>#N/A</v>
       </c>
       <c r="AW103" s="156" t="e">
@@ -39030,7 +39071,7 @@
         <v>#N/A</v>
       </c>
       <c r="AX103" s="156" t="e">
-        <f aca="false">([1]!Table2[[#this row],[object_a_._head_time]]/([1]!Table2[[#this row],[object_a_._head_time]]+[1]!Table2[[#this row],[object_b_._head_time]]))*100</f>
+        <f aca="false">([1]!table2[[#this row],[object_a_._head_time]]/([1]!table2[[#this row],[object_a_._head_time]]+[1]!table2[[#this row],[object_b_._head_time]]))*100</f>
         <v>#N/A</v>
       </c>
       <c r="AY103" s="108" t="s">
@@ -39058,8 +39099,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
